--- a/assets/docs/boq-hamra.xlsx
+++ b/assets/docs/boq-hamra.xlsx
@@ -2646,7 +2646,9 @@
         <v>26</v>
       </c>
       <c r="F3" s="35"/>
-      <c r="G3" s="37"/>
+      <c r="G3" s="37">
+        <f t="shared" ref="G3:G6" si="1">D3*F3</f>
+      </c>
       <c r="H3" s="40"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
@@ -2686,7 +2688,9 @@
         <v>26</v>
       </c>
       <c r="F4" s="35"/>
-      <c r="G4" s="37"/>
+      <c r="G4" s="37">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H4" s="40" t="e">
         <v>#VALUE!</v>
       </c>
@@ -2728,7 +2732,9 @@
         <v>26</v>
       </c>
       <c r="F5" s="35"/>
-      <c r="G5" s="37"/>
+      <c r="G5" s="37">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H5" s="40" t="e">
         <v>#VALUE!</v>
       </c>
@@ -2770,7 +2776,9 @@
         <v>26</v>
       </c>
       <c r="F6" s="35"/>
-      <c r="G6" s="37"/>
+      <c r="G6" s="37">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H6" s="40"/>
       <c r="I6" s="42"/>
       <c r="J6" s="42"/>
@@ -2802,7 +2810,9 @@
       <c r="D7" s="51"/>
       <c r="E7" s="49"/>
       <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
+      <c r="G7" s="52">
+        <f>SUM(G3:G6)</f>
+      </c>
       <c r="H7" s="54"/>
       <c r="I7" s="55"/>
       <c r="J7" s="55"/>
@@ -2876,7 +2886,9 @@
         <v>20</v>
       </c>
       <c r="F9" s="45"/>
-      <c r="G9" s="46"/>
+      <c r="G9" s="46">
+        <f>D9*F9</f>
+      </c>
       <c r="H9" s="68"/>
       <c r="I9" s="55"/>
       <c r="J9" s="55"/>
@@ -2908,7 +2920,9 @@
       <c r="D10" s="49"/>
       <c r="E10" s="49"/>
       <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
+      <c r="G10" s="52">
+        <f>G9</f>
+      </c>
       <c r="H10" s="54"/>
       <c r="I10" s="55"/>
       <c r="J10" s="55"/>
@@ -2982,7 +2996,9 @@
         <v>20</v>
       </c>
       <c r="F12" s="45"/>
-      <c r="G12" s="46"/>
+      <c r="G12" s="46">
+        <f>D12*F12</f>
+      </c>
       <c r="H12" s="68"/>
       <c r="I12" s="55"/>
       <c r="J12" s="55"/>
@@ -3014,7 +3030,9 @@
       <c r="D13" s="51"/>
       <c r="E13" s="49"/>
       <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
+      <c r="G13" s="52">
+        <f>G12</f>
+      </c>
       <c r="H13" s="54"/>
       <c r="I13" s="55"/>
       <c r="J13" s="55"/>
@@ -3088,7 +3106,9 @@
         <v>40</v>
       </c>
       <c r="F15" s="35"/>
-      <c r="G15" s="37"/>
+      <c r="G15" s="37">
+        <f>D15*F15</f>
+      </c>
       <c r="H15" s="40" t="e">
         <v>#VALUE!</v>
       </c>
@@ -3122,7 +3142,9 @@
       <c r="D16" s="51"/>
       <c r="E16" s="49"/>
       <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
+      <c r="G16" s="52">
+        <f>G15</f>
+      </c>
       <c r="H16" s="54"/>
       <c r="I16" s="55"/>
       <c r="J16" s="55"/>
@@ -3196,7 +3218,9 @@
         <v>40</v>
       </c>
       <c r="F18" s="83"/>
-      <c r="G18" s="84"/>
+      <c r="G18" s="84">
+        <f t="shared" ref="G18:G19" si="2">D18*F18</f>
+      </c>
       <c r="H18" s="68" t="e">
         <v>#VALUE!</v>
       </c>
@@ -3218,7 +3242,9 @@
         <v>40</v>
       </c>
       <c r="F19" s="83"/>
-      <c r="G19" s="84"/>
+      <c r="G19" s="84">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H19" s="68" t="e">
         <v>#VALUE!</v>
       </c>
@@ -3232,7 +3258,9 @@
       <c r="D20" s="51"/>
       <c r="E20" s="49"/>
       <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
+      <c r="G20" s="52">
+        <f>SUM(G18:G19)</f>
+      </c>
       <c r="H20" s="54"/>
       <c r="I20" s="55"/>
       <c r="J20" s="55"/>
@@ -3264,7 +3292,9 @@
       <c r="D21" s="88"/>
       <c r="E21" s="86"/>
       <c r="F21" s="86"/>
-      <c r="G21" s="90"/>
+      <c r="G21" s="90">
+        <f>G7+G10+G13+G16+G20</f>
+      </c>
       <c r="H21" s="85"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -10226,7 +10256,9 @@
         <v>20</v>
       </c>
       <c r="F3" s="28"/>
-      <c r="G3" s="31"/>
+      <c r="G3" s="31">
+        <f t="shared" ref="G3:G13" si="1">D3*F3</f>
+      </c>
       <c r="H3" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10248,7 +10280,9 @@
         <v>20</v>
       </c>
       <c r="F4" s="28"/>
-      <c r="G4" s="31"/>
+      <c r="G4" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H4" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10270,7 +10304,9 @@
         <v>20</v>
       </c>
       <c r="F5" s="45"/>
-      <c r="G5" s="46"/>
+      <c r="G5" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H5" s="47" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10292,7 +10328,9 @@
         <v>20</v>
       </c>
       <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
+      <c r="G6" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H6" s="47" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10314,7 +10352,9 @@
         <v>20</v>
       </c>
       <c r="F7" s="28"/>
-      <c r="G7" s="31"/>
+      <c r="G7" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H7" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10336,7 +10376,9 @@
         <v>40</v>
       </c>
       <c r="F8" s="45"/>
-      <c r="G8" s="46"/>
+      <c r="G8" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H8" s="47" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10356,7 +10398,9 @@
         <v>43</v>
       </c>
       <c r="F9" s="45"/>
-      <c r="G9" s="46"/>
+      <c r="G9" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H9" s="47" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10378,7 +10422,9 @@
         <v>20</v>
       </c>
       <c r="F10" s="45"/>
-      <c r="G10" s="46"/>
+      <c r="G10" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H10" s="47" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10400,7 +10446,9 @@
         <v>20</v>
       </c>
       <c r="F11" s="45"/>
-      <c r="G11" s="46"/>
+      <c r="G11" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H11" s="47" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10422,7 +10470,9 @@
         <v>51</v>
       </c>
       <c r="F12" s="45"/>
-      <c r="G12" s="46"/>
+      <c r="G12" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H12" s="47" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10444,7 +10494,9 @@
         <v>20</v>
       </c>
       <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="G13" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H13" s="47"/>
     </row>
     <row r="14">
@@ -10456,7 +10508,9 @@
       <c r="D14" s="51"/>
       <c r="E14" s="49"/>
       <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
+      <c r="G14" s="52">
+        <f>SUM(G3:G13)</f>
+      </c>
       <c r="H14" s="61"/>
       <c r="I14" s="55"/>
       <c r="J14" s="55"/>
@@ -10530,7 +10584,9 @@
         <v>20</v>
       </c>
       <c r="F16" s="28"/>
-      <c r="G16" s="31"/>
+      <c r="G16" s="31">
+        <f>D16*F16</f>
+      </c>
       <c r="H16" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10656,7 +10712,9 @@
         <v>20</v>
       </c>
       <c r="F19" s="28"/>
-      <c r="G19" s="31"/>
+      <c r="G19" s="31">
+        <f>D19*F19</f>
+      </c>
       <c r="H19" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10782,7 +10840,9 @@
         <v>20</v>
       </c>
       <c r="F22" s="28"/>
-      <c r="G22" s="31"/>
+      <c r="G22" s="31">
+        <f t="shared" ref="G22:G24" si="2">D22*F22</f>
+      </c>
       <c r="H22" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10824,7 +10884,9 @@
         <v>20</v>
       </c>
       <c r="F23" s="28"/>
-      <c r="G23" s="31"/>
+      <c r="G23" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H23" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10866,7 +10928,9 @@
         <v>20</v>
       </c>
       <c r="F24" s="28"/>
-      <c r="G24" s="31"/>
+      <c r="G24" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H24" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10900,7 +10964,9 @@
       <c r="D25" s="78"/>
       <c r="E25" s="76"/>
       <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
+      <c r="G25" s="79">
+        <f>SUM(G16:G24)</f>
+      </c>
       <c r="H25" s="80"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -10912,7 +10978,9 @@
       <c r="D26" s="73"/>
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
-      <c r="G26" s="74"/>
+      <c r="G26" s="74">
+        <f>G14+G25</f>
+      </c>
       <c r="H26" s="70"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
@@ -13941,7 +14009,9 @@
         <v>20</v>
       </c>
       <c r="F3" s="28"/>
-      <c r="G3" s="31"/>
+      <c r="G3" s="31">
+        <f>D3*F3</f>
+      </c>
       <c r="H3" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -14067,7 +14137,9 @@
         <v>20</v>
       </c>
       <c r="F6" s="28"/>
-      <c r="G6" s="31"/>
+      <c r="G6" s="31">
+        <f>D6*F6</f>
+      </c>
       <c r="H6" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -14173,7 +14245,9 @@
         <v>20</v>
       </c>
       <c r="F9" s="28"/>
-      <c r="G9" s="31"/>
+      <c r="G9" s="31">
+        <f t="shared" ref="G9:G11" si="1">D9*F9</f>
+      </c>
       <c r="H9" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -14195,7 +14269,9 @@
         <v>40</v>
       </c>
       <c r="F10" s="28"/>
-      <c r="G10" s="31"/>
+      <c r="G10" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H10" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -14217,7 +14293,9 @@
         <v>20</v>
       </c>
       <c r="F11" s="28"/>
-      <c r="G11" s="31"/>
+      <c r="G11" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H11" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -14251,7 +14329,9 @@
       <c r="D12" s="51"/>
       <c r="E12" s="49"/>
       <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
+      <c r="G12" s="52">
+        <f>SUM(G8:G11)</f>
+      </c>
       <c r="H12" s="52"/>
     </row>
     <row r="13">
@@ -14305,7 +14385,9 @@
         <v>20</v>
       </c>
       <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="G14" s="46">
+        <f t="shared" ref="G14:G15" si="2">D14*F14</f>
+      </c>
       <c r="H14" s="46" t="e">
         <v>#VALUE!</v>
       </c>
@@ -14327,7 +14409,9 @@
         <v>20</v>
       </c>
       <c r="F15" s="45"/>
-      <c r="G15" s="46"/>
+      <c r="G15" s="46">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H15" s="47" t="e">
         <v>#VALUE!</v>
       </c>
@@ -14363,7 +14447,9 @@
       <c r="D17" s="51"/>
       <c r="E17" s="49"/>
       <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
+      <c r="G17" s="52">
+        <f>SUM(G14)</f>
+      </c>
       <c r="H17" s="52"/>
     </row>
     <row r="18">
@@ -14375,7 +14461,9 @@
       <c r="D18" s="73"/>
       <c r="E18" s="70"/>
       <c r="F18" s="70"/>
-      <c r="G18" s="74"/>
+      <c r="G18" s="74">
+        <f>G12+G17</f>
+      </c>
       <c r="H18" s="74"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -17427,7 +17515,9 @@
         <v>40</v>
       </c>
       <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
+      <c r="G3" s="46">
+        <f t="shared" ref="G3:G11" si="1">D3*F3</f>
+      </c>
       <c r="H3" s="46" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17449,7 +17539,9 @@
         <v>20</v>
       </c>
       <c r="F4" s="28"/>
-      <c r="G4" s="31"/>
+      <c r="G4" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H4" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17471,7 +17563,9 @@
         <v>20</v>
       </c>
       <c r="F5" s="28"/>
-      <c r="G5" s="31"/>
+      <c r="G5" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H5" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17493,7 +17587,9 @@
         <v>51</v>
       </c>
       <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
+      <c r="G6" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H6" s="46" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17515,7 +17611,9 @@
         <v>40</v>
       </c>
       <c r="F7" s="45"/>
-      <c r="G7" s="46"/>
+      <c r="G7" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H7" s="46" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17537,7 +17635,9 @@
         <v>20</v>
       </c>
       <c r="F8" s="28"/>
-      <c r="G8" s="31"/>
+      <c r="G8" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H8" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17559,7 +17659,9 @@
         <v>20</v>
       </c>
       <c r="F9" s="28"/>
-      <c r="G9" s="31"/>
+      <c r="G9" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H9" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17581,7 +17683,9 @@
         <v>20</v>
       </c>
       <c r="F10" s="28"/>
-      <c r="G10" s="31"/>
+      <c r="G10" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H10" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17603,7 +17707,9 @@
         <v>20</v>
       </c>
       <c r="F11" s="45"/>
-      <c r="G11" s="46"/>
+      <c r="G11" s="46">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H11" s="46" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17617,7 +17723,9 @@
       <c r="D12" s="51"/>
       <c r="E12" s="49"/>
       <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
+      <c r="G12" s="52">
+        <f>SUM(G3:G11)</f>
+      </c>
       <c r="H12" s="52"/>
     </row>
     <row r="13">
@@ -17671,7 +17779,9 @@
         <v>51</v>
       </c>
       <c r="F14" s="28"/>
-      <c r="G14" s="31"/>
+      <c r="G14" s="31">
+        <f>D14*F14</f>
+      </c>
       <c r="H14" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -17685,7 +17795,9 @@
       <c r="D15" s="51"/>
       <c r="E15" s="49"/>
       <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
+      <c r="G15" s="52">
+        <f>G14</f>
+      </c>
       <c r="H15" s="52"/>
     </row>
     <row r="16">
@@ -17697,7 +17809,9 @@
       <c r="D16" s="73"/>
       <c r="E16" s="70"/>
       <c r="F16" s="70"/>
-      <c r="G16" s="74"/>
+      <c r="G16" s="74">
+        <f>G12+G15</f>
+      </c>
       <c r="H16" s="74"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -21739,7 +21853,9 @@
         <v>51</v>
       </c>
       <c r="F3" s="45"/>
-      <c r="G3" s="46" t="str"/>
+      <c r="G3" s="46" t="str">
+        <f t="shared" ref="G3:G4" si="1">G2</f>
+      </c>
       <c r="H3" s="46" t="e">
         <v>#VALUE!</v>
       </c>
@@ -21780,7 +21896,9 @@
       <c r="E4" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="46" t="str"/>
+      <c r="G4" s="46" t="str">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H4" s="96" t="e">
         <v>#VALUE!</v>
       </c>
@@ -21810,7 +21928,9 @@
       <c r="D5" s="51"/>
       <c r="E5" s="49"/>
       <c r="F5" s="52"/>
-      <c r="G5" s="52" t="str"/>
+      <c r="G5" s="52" t="str">
+        <f>G3</f>
+      </c>
       <c r="H5" s="52"/>
     </row>
     <row r="6">
@@ -21864,7 +21984,9 @@
         <v>20</v>
       </c>
       <c r="F7" s="28"/>
-      <c r="G7" s="31"/>
+      <c r="G7" s="31">
+        <f t="shared" ref="G7:G9" si="2">D7*F7</f>
+      </c>
       <c r="H7" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -21886,7 +22008,9 @@
         <v>20</v>
       </c>
       <c r="F8" s="28"/>
-      <c r="G8" s="31"/>
+      <c r="G8" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H8" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -21908,7 +22032,9 @@
         <v>20</v>
       </c>
       <c r="F9" s="28"/>
-      <c r="G9" s="31"/>
+      <c r="G9" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H9" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -21922,7 +22048,9 @@
       <c r="D10" s="51"/>
       <c r="E10" s="49"/>
       <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
+      <c r="G10" s="52">
+        <f>SUM(G7:G9)</f>
+      </c>
       <c r="H10" s="52"/>
     </row>
     <row r="11">
@@ -21976,7 +22104,9 @@
         <v>20</v>
       </c>
       <c r="F12" s="28"/>
-      <c r="G12" s="31"/>
+      <c r="G12" s="31">
+        <f>D12*F12</f>
+      </c>
       <c r="H12" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -21990,7 +22120,9 @@
       <c r="D13" s="51"/>
       <c r="E13" s="49"/>
       <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
+      <c r="G13" s="52">
+        <f>SUM(G11:G12)</f>
+      </c>
       <c r="H13" s="52"/>
     </row>
     <row r="14">
@@ -22044,7 +22176,9 @@
         <v>20</v>
       </c>
       <c r="F15" s="28"/>
-      <c r="G15" s="31"/>
+      <c r="G15" s="31">
+        <f t="shared" ref="G15:G16" si="3">D15*F15</f>
+      </c>
       <c r="H15" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -22086,7 +22220,9 @@
         <v>20</v>
       </c>
       <c r="F16" s="28"/>
-      <c r="G16" s="31"/>
+      <c r="G16" s="31">
+        <f t="shared" si="3"/>
+      </c>
       <c r="H16" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -22100,7 +22236,9 @@
       <c r="D17" s="51"/>
       <c r="E17" s="49"/>
       <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
+      <c r="G17" s="52">
+        <f>SUM(G14:G16)</f>
+      </c>
       <c r="H17" s="52"/>
     </row>
     <row r="18">
@@ -22154,7 +22292,9 @@
         <v>20</v>
       </c>
       <c r="F19" s="106"/>
-      <c r="G19" s="107"/>
+      <c r="G19" s="107">
+        <f>D19*F20</f>
+      </c>
       <c r="H19" s="108" t="e">
         <v>#VALUE!</v>
       </c>
@@ -22208,7 +22348,9 @@
         <v>20</v>
       </c>
       <c r="F21" s="28"/>
-      <c r="G21" s="31"/>
+      <c r="G21" s="31">
+        <f t="shared" ref="G21:G22" si="4">D21*F21</f>
+      </c>
       <c r="H21" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -22230,7 +22372,9 @@
         <v>51</v>
       </c>
       <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
+      <c r="G22" s="31">
+        <f t="shared" si="4"/>
+      </c>
       <c r="H22" s="31" t="e">
         <v>#VALUE!</v>
       </c>
@@ -22244,7 +22388,9 @@
       <c r="D23" s="51"/>
       <c r="E23" s="49"/>
       <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
+      <c r="G23" s="52">
+        <f>SUM(G19:G22)</f>
+      </c>
       <c r="H23" s="52"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -22256,7 +22402,9 @@
       <c r="D24" s="73"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
-      <c r="G24" s="74"/>
+      <c r="G24" s="74">
+        <f>G5+G10+G13+G17+G23</f>
+      </c>
       <c r="H24" s="70"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -25289,7 +25437,9 @@
         <v>40</v>
       </c>
       <c r="F4" s="28"/>
-      <c r="G4" s="31"/>
+      <c r="G4" s="31">
+        <f t="shared" ref="G4:G9" si="1">D4*F4</f>
+      </c>
       <c r="H4" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25311,7 +25461,9 @@
         <v>20</v>
       </c>
       <c r="F5" s="28"/>
-      <c r="G5" s="31"/>
+      <c r="G5" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H5" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25333,7 +25485,9 @@
         <v>20</v>
       </c>
       <c r="F6" s="28"/>
-      <c r="G6" s="31"/>
+      <c r="G6" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H6" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25355,7 +25509,9 @@
         <v>40</v>
       </c>
       <c r="F7" s="28"/>
-      <c r="G7" s="31"/>
+      <c r="G7" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H7" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25377,7 +25533,9 @@
         <v>40</v>
       </c>
       <c r="F8" s="28"/>
-      <c r="G8" s="31"/>
+      <c r="G8" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H8" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25399,7 +25557,9 @@
         <v>20</v>
       </c>
       <c r="F9" s="28"/>
-      <c r="G9" s="31"/>
+      <c r="G9" s="31">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H9" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25545,7 +25705,9 @@
       <c r="D16" s="100"/>
       <c r="E16" s="49"/>
       <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
+      <c r="G16" s="52">
+        <f>SUM(G4:G15)</f>
+      </c>
       <c r="H16" s="61"/>
     </row>
     <row r="17" ht="27.0" customHeight="1">
@@ -25589,7 +25751,9 @@
         <v>40</v>
       </c>
       <c r="F19" s="28"/>
-      <c r="G19" s="31"/>
+      <c r="G19" s="31">
+        <f t="shared" ref="G19:G24" si="2">D19*F19</f>
+      </c>
       <c r="H19" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25611,7 +25775,9 @@
         <v>20</v>
       </c>
       <c r="F20" s="28"/>
-      <c r="G20" s="31"/>
+      <c r="G20" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H20" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25633,7 +25799,9 @@
         <v>20</v>
       </c>
       <c r="F21" s="28"/>
-      <c r="G21" s="31"/>
+      <c r="G21" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H21" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25655,7 +25823,9 @@
         <v>40</v>
       </c>
       <c r="F22" s="28"/>
-      <c r="G22" s="31"/>
+      <c r="G22" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H22" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25677,7 +25847,9 @@
         <v>40</v>
       </c>
       <c r="F23" s="28"/>
-      <c r="G23" s="31"/>
+      <c r="G23" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H23" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25699,7 +25871,9 @@
         <v>20</v>
       </c>
       <c r="F24" s="28"/>
-      <c r="G24" s="31"/>
+      <c r="G24" s="31">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H24" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -25845,7 +26019,9 @@
       <c r="D31" s="100"/>
       <c r="E31" s="49"/>
       <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
+      <c r="G31" s="52">
+        <f>SUM(G19:G30)</f>
+      </c>
       <c r="H31" s="61"/>
     </row>
     <row r="32" ht="14.25" hidden="1" customHeight="1"/>
